--- a/data.mn/public/datasets/population-total-mongolia.xlsx
+++ b/data.mn/public/datasets/population-total-mongolia.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Data" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="English" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Монгол" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -763,4 +764,362 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B42"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>он</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>утга</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1956</v>
+      </c>
+      <c r="B2" t="n">
+        <v>845481</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1963</v>
+      </c>
+      <c r="B3" t="n">
+        <v>1017158</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>1969</v>
+      </c>
+      <c r="B4" t="n">
+        <v>1197595</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>1979</v>
+      </c>
+      <c r="B5" t="n">
+        <v>1595006</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>1989</v>
+      </c>
+      <c r="B6" t="n">
+        <v>2043954</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>1990</v>
+      </c>
+      <c r="B7" t="n">
+        <v>2153466</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>1991</v>
+      </c>
+      <c r="B8" t="n">
+        <v>2177217</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>1992</v>
+      </c>
+      <c r="B9" t="n">
+        <v>2158362</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>1993</v>
+      </c>
+      <c r="B10" t="n">
+        <v>2171898</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>1994</v>
+      </c>
+      <c r="B11" t="n">
+        <v>2206892</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>1995</v>
+      </c>
+      <c r="B12" t="n">
+        <v>2242998</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>1996</v>
+      </c>
+      <c r="B13" t="n">
+        <v>2276016</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>1997</v>
+      </c>
+      <c r="B14" t="n">
+        <v>2307484</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>1998</v>
+      </c>
+      <c r="B15" t="n">
+        <v>2340134</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>1999</v>
+      </c>
+      <c r="B16" t="n">
+        <v>2373493</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>2000</v>
+      </c>
+      <c r="B17" t="n">
+        <v>2403105</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>2001</v>
+      </c>
+      <c r="B18" t="n">
+        <v>2432397</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>2002</v>
+      </c>
+      <c r="B19" t="n">
+        <v>2465657</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>2003</v>
+      </c>
+      <c r="B20" t="n">
+        <v>2495091</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>2004</v>
+      </c>
+      <c r="B21" t="n">
+        <v>2521733</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>2005</v>
+      </c>
+      <c r="B22" t="n">
+        <v>2551081</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>2006</v>
+      </c>
+      <c r="B23" t="n">
+        <v>2583254</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>2007</v>
+      </c>
+      <c r="B24" t="n">
+        <v>2620446</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>2008</v>
+      </c>
+      <c r="B25" t="n">
+        <v>2665955</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>2009</v>
+      </c>
+      <c r="B26" t="n">
+        <v>2716275</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>2010</v>
+      </c>
+      <c r="B27" t="n">
+        <v>2760968</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>2011</v>
+      </c>
+      <c r="B28" t="n">
+        <v>2811666</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>2012</v>
+      </c>
+      <c r="B29" t="n">
+        <v>2867744</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>2013</v>
+      </c>
+      <c r="B30" t="n">
+        <v>2930277</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>2014</v>
+      </c>
+      <c r="B31" t="n">
+        <v>2995949</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>2015</v>
+      </c>
+      <c r="B32" t="n">
+        <v>3057778</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>2016</v>
+      </c>
+      <c r="B33" t="n">
+        <v>3119935</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>2017</v>
+      </c>
+      <c r="B34" t="n">
+        <v>3177899</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>2018</v>
+      </c>
+      <c r="B35" t="n">
+        <v>3238479</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>2019</v>
+      </c>
+      <c r="B36" t="n">
+        <v>3296866</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>2020</v>
+      </c>
+      <c r="B37" t="n">
+        <v>3367257</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>2021</v>
+      </c>
+      <c r="B38" t="n">
+        <v>3419654</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B39" t="n">
+        <v>3467263</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B40" t="n">
+        <v>3514456</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B41" t="n">
+        <v>3554550</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B42" t="n">
+        <v>3591120</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>